--- a/Fig2/excel/SolarDistributedAll.xlsx
+++ b/Fig2/excel/SolarDistributedAll.xlsx
@@ -1,40 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xiangdebin/Library/Mobile Documents/com~apple~CloudDocs/research/项目/光伏论文/光伏画图数据0117/PVplotHub/Fig2/excel/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AD6F3C-D46F-5546-BBB0-683A1133F77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="4880" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+  <si>
+    <t>集中式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>光照</t>
-  </si>
-  <si>
-    <t>集中式装机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>分布式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>总计</t>
+    <r>
+      <t>China-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集中式</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,32 +96,348 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C141"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U140"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" ht="17">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>2700</v>
       </c>
@@ -90,10 +445,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>7.4977046618027605e-05</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>7.4977046618027605E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2750</v>
       </c>
@@ -101,10 +456,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>2.24465296927476e-06</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>2.24465296927476E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2850</v>
       </c>
@@ -112,10 +467,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.00046191947502046299</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>4.6191947502046299E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>2900</v>
       </c>
@@ -123,10 +478,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.00076324487831475995</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>7.6324487831475995E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>2950</v>
       </c>
@@ -134,10 +489,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.0015727797334855</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>1.5727797334855E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>3000</v>
       </c>
@@ -145,43 +500,43 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.024532624594358999</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>2.4532624594358999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>3050</v>
       </c>
       <c r="B8">
-        <v>0.0051237687254440797</v>
+        <v>5.1237687254440797E-3</v>
       </c>
       <c r="C8">
-        <v>0.022873766703451402</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>2.2873766703451402E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>3100</v>
       </c>
       <c r="B9">
-        <v>0.011568431899225899</v>
+        <v>1.1568431899225899E-2</v>
       </c>
       <c r="C9">
-        <v>0.020855448339225102</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>2.0855448339225102E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>3150</v>
       </c>
       <c r="B10">
-        <v>0.098980755929768099</v>
+        <v>9.8980755929768099E-2</v>
       </c>
       <c r="C10">
-        <v>0.030274953597447699</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>3.0274953597447699E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>3200</v>
       </c>
@@ -189,10 +544,10 @@
         <v>0.16800621978525099</v>
       </c>
       <c r="C11">
-        <v>0.041765968971776202</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>4.1765968971776202E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>3250</v>
       </c>
@@ -200,10 +555,10 @@
         <v>0.60736816413822503</v>
       </c>
       <c r="C12">
-        <v>0.068192077212683902</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>6.8192077212683902E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>3300</v>
       </c>
@@ -211,10 +566,10 @@
         <v>1.0173913570700099</v>
       </c>
       <c r="C13">
-        <v>0.092240748854028803</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>9.2240748854028803E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>3350</v>
       </c>
@@ -225,7 +580,7 @@
         <v>0.18002961561629099</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>3400</v>
       </c>
@@ -236,7 +591,7 @@
         <v>0.14757904038403599</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>3450</v>
       </c>
@@ -247,7 +602,7 @@
         <v>0.20786096433932</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>3500</v>
       </c>
@@ -258,7 +613,7 @@
         <v>0.199097241433176</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>3550</v>
       </c>
@@ -269,7 +624,7 @@
         <v>0.188109273775564</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>3600</v>
       </c>
@@ -280,7 +635,7 @@
         <v>0.13795486836346699</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>3650</v>
       </c>
@@ -291,7 +646,7 @@
         <v>0.118829439482625</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>3700</v>
       </c>
@@ -301,8 +656,14 @@
       <c r="C21">
         <v>1.1016222503317099</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="J21">
+        <v>0.11304</v>
+      </c>
+      <c r="K21">
+        <v>8.2900000000000005E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>3750</v>
       </c>
@@ -312,8 +673,14 @@
       <c r="C22">
         <v>2.1663158653229999</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="J22">
+        <v>2.8250500000000001</v>
+      </c>
+      <c r="K22">
+        <v>0.93859000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>3800</v>
       </c>
@@ -323,8 +690,14 @@
       <c r="C23">
         <v>1.31459128803406</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="J23">
+        <v>2.8532999999999999</v>
+      </c>
+      <c r="K23">
+        <v>0.86736000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>3850</v>
       </c>
@@ -334,8 +707,14 @@
       <c r="C24">
         <v>0.67719199622134496</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="J24">
+        <v>4.8680300000000001</v>
+      </c>
+      <c r="K24">
+        <v>0.31597999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>3900</v>
       </c>
@@ -345,8 +724,20 @@
       <c r="C25">
         <v>0.74354407744248896</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1.8189399999999999E-4</v>
+      </c>
+      <c r="J25">
+        <v>6.0354700000000001</v>
+      </c>
+      <c r="K25">
+        <v>0.38590999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>3950</v>
       </c>
@@ -356,8 +747,20 @@
       <c r="C26">
         <v>0.58027589294058901</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="D26">
+        <v>5.8369999999999998E-2</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2.9211200000000002E-4</v>
+      </c>
+      <c r="J26">
+        <v>7.0156599999999996</v>
+      </c>
+      <c r="K26">
+        <v>0.34384999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>4000</v>
       </c>
@@ -367,8 +770,20 @@
       <c r="C27">
         <v>0.851729626967762</v>
       </c>
-    </row>
-    <row r="28">
+      <c r="D27">
+        <v>1.192E-2</v>
+      </c>
+      <c r="E27" s="3">
+        <v>8.2991599999999999E-4</v>
+      </c>
+      <c r="J27">
+        <v>6.57111</v>
+      </c>
+      <c r="K27">
+        <v>0.42777999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>4050</v>
       </c>
@@ -378,8 +793,20 @@
       <c r="C28">
         <v>1.07576096328066</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>2.6919999999999999E-2</v>
+      </c>
+      <c r="J28">
+        <v>7.1227400000000003</v>
+      </c>
+      <c r="K28">
+        <v>0.55086999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>4100</v>
       </c>
@@ -389,8 +816,20 @@
       <c r="C29">
         <v>1.04276554637038</v>
       </c>
-    </row>
-    <row r="30">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1.6449999999999999E-2</v>
+      </c>
+      <c r="J29">
+        <v>12.261380000000001</v>
+      </c>
+      <c r="K29">
+        <v>0.79259000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>4150</v>
       </c>
@@ -400,8 +839,20 @@
       <c r="C30">
         <v>1.6452326418094201</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>1.261E-2</v>
+      </c>
+      <c r="J30">
+        <v>11.274509999999999</v>
+      </c>
+      <c r="K30">
+        <v>1.3039799999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>4200</v>
       </c>
@@ -411,8 +862,20 @@
       <c r="C31">
         <v>0.660540977553424</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="D31">
+        <v>1.0789999999999999E-2</v>
+      </c>
+      <c r="E31">
+        <v>1.5640000000000001E-2</v>
+      </c>
+      <c r="J31">
+        <v>1.3766499999999999</v>
+      </c>
+      <c r="K31">
+        <v>0.41063</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>4250</v>
       </c>
@@ -422,8 +885,20 @@
       <c r="C32">
         <v>1.10863594725644</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="D32">
+        <v>1.0959999999999999E-2</v>
+      </c>
+      <c r="E32">
+        <v>4.1209999999999997E-2</v>
+      </c>
+      <c r="J32">
+        <v>2.4207700000000001</v>
+      </c>
+      <c r="K32">
+        <v>0.62653999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33">
         <v>4300</v>
       </c>
@@ -433,8 +908,26 @@
       <c r="C33">
         <v>1.33885598474937</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="D33">
+        <v>1.933E-2</v>
+      </c>
+      <c r="E33">
+        <v>9.4390000000000002E-2</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>4.4200000000000003E-3</v>
+      </c>
+      <c r="J33">
+        <v>4.2631100000000002</v>
+      </c>
+      <c r="K33">
+        <v>0.87326999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34">
         <v>4350</v>
       </c>
@@ -444,8 +937,26 @@
       <c r="C34">
         <v>0.81152234799260703</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="D34">
+        <v>0.41066999999999998</v>
+      </c>
+      <c r="E34">
+        <v>0.1459</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>4.9079999999999999E-2</v>
+      </c>
+      <c r="J34">
+        <v>1.4971000000000001</v>
+      </c>
+      <c r="K34">
+        <v>0.16374</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35">
         <v>4400</v>
       </c>
@@ -455,8 +966,20 @@
       <c r="C35">
         <v>0.45510388041382399</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="D35">
+        <v>0.50380999999999998</v>
+      </c>
+      <c r="E35">
+        <v>0.19911000000000001</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1.0290000000000001E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36">
         <v>4450</v>
       </c>
@@ -466,8 +989,20 @@
       <c r="C36">
         <v>0.38175205939981699</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="D36">
+        <v>0.38729999999999998</v>
+      </c>
+      <c r="E36">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="F36" s="3">
+        <v>4.8037200000000001E-4</v>
+      </c>
+      <c r="G36">
+        <v>3.1300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37">
         <v>4500</v>
       </c>
@@ -477,8 +1012,20 @@
       <c r="C37">
         <v>0.54480032106859599</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="D37">
+        <v>0.90578999999999998</v>
+      </c>
+      <c r="E37">
+        <v>7.4950000000000003E-2</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>2.8979999999999999E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38">
         <v>4550</v>
       </c>
@@ -488,8 +1035,20 @@
       <c r="C38">
         <v>0.73154384419449103</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="D38">
+        <v>0.44794</v>
+      </c>
+      <c r="E38">
+        <v>2.3810000000000001E-2</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>2.8590000000000001E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39">
         <v>4600</v>
       </c>
@@ -499,8 +1058,20 @@
       <c r="C39">
         <v>0.86875521237119302</v>
       </c>
-    </row>
-    <row r="40">
+      <c r="D39">
+        <v>3.3424100000000001</v>
+      </c>
+      <c r="E39">
+        <v>0.10423</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>4.9300000000000004E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40">
         <v>4650</v>
       </c>
@@ -510,8 +1081,26 @@
       <c r="C40">
         <v>1.0421560329099899</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="D40">
+        <v>1.84537</v>
+      </c>
+      <c r="E40">
+        <v>8.4709999999999994E-2</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>1.5100000000000001E-3</v>
+      </c>
+      <c r="L40">
+        <v>1.4590000000000001E-2</v>
+      </c>
+      <c r="M40">
+        <v>3.0599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41">
         <v>4700</v>
       </c>
@@ -521,8 +1110,26 @@
       <c r="C41">
         <v>0.80898850008173695</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="D41">
+        <v>3.3159399999999999</v>
+      </c>
+      <c r="E41">
+        <v>4.7010000000000003E-2</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="L41">
+        <v>1.15696</v>
+      </c>
+      <c r="M41">
+        <v>5.2729999999999999E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42">
         <v>4750</v>
       </c>
@@ -532,8 +1139,32 @@
       <c r="C42">
         <v>1.0418422034734101</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="D42">
+        <v>1.8591</v>
+      </c>
+      <c r="E42">
+        <v>0.44524000000000002</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3.2025400000000001E-4</v>
+      </c>
+      <c r="G42">
+        <v>2.0799999999999998E-3</v>
+      </c>
+      <c r="L42">
+        <v>1.16757</v>
+      </c>
+      <c r="M42">
+        <v>4.8320000000000002E-2</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>2.1530000000000001E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43">
         <v>4800</v>
       </c>
@@ -543,8 +1174,32 @@
       <c r="C43">
         <v>2.3321919987001198</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="D43">
+        <v>6.5950699999999998</v>
+      </c>
+      <c r="E43">
+        <v>1.58741</v>
+      </c>
+      <c r="F43">
+        <v>9.2450000000000004E-2</v>
+      </c>
+      <c r="G43">
+        <v>2.1099999999999999E-3</v>
+      </c>
+      <c r="L43">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="M43">
+        <v>0.12526000000000001</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>2.5579999999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44">
         <v>4850</v>
       </c>
@@ -554,8 +1209,32 @@
       <c r="C44">
         <v>2.88623774323159</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="D44">
+        <v>9.2299100000000003</v>
+      </c>
+      <c r="E44">
+        <v>2.11002</v>
+      </c>
+      <c r="F44">
+        <v>0.35664000000000001</v>
+      </c>
+      <c r="G44">
+        <v>5.1729999999999998E-2</v>
+      </c>
+      <c r="L44">
+        <v>1.3923399999999999</v>
+      </c>
+      <c r="M44">
+        <v>9.2850000000000002E-2</v>
+      </c>
+      <c r="N44">
+        <v>1.3600000000000001E-3</v>
+      </c>
+      <c r="O44">
+        <v>4.7350000000000003E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45">
         <v>4900</v>
       </c>
@@ -565,8 +1244,32 @@
       <c r="C45">
         <v>2.3509383200464402</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="D45">
+        <v>7.6598300000000004</v>
+      </c>
+      <c r="E45">
+        <v>1.7903</v>
+      </c>
+      <c r="F45">
+        <v>0.71052000000000004</v>
+      </c>
+      <c r="G45">
+        <v>4.4850000000000001E-2</v>
+      </c>
+      <c r="L45">
+        <v>1.01267</v>
+      </c>
+      <c r="M45">
+        <v>0.14731</v>
+      </c>
+      <c r="N45">
+        <v>1.7579999999999998E-2</v>
+      </c>
+      <c r="O45">
+        <v>1.9619999999999999E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46">
         <v>4950</v>
       </c>
@@ -576,8 +1279,32 @@
       <c r="C46">
         <v>2.8011292380749402</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="D46">
+        <v>6.7736299999999998</v>
+      </c>
+      <c r="E46">
+        <v>1.5347599999999999</v>
+      </c>
+      <c r="F46">
+        <v>0.78918999999999995</v>
+      </c>
+      <c r="G46">
+        <v>7.2270000000000001E-2</v>
+      </c>
+      <c r="L46">
+        <v>6.2200199999999999</v>
+      </c>
+      <c r="M46">
+        <v>0.83374999999999999</v>
+      </c>
+      <c r="N46">
+        <v>2.2399999999999998E-3</v>
+      </c>
+      <c r="O46">
+        <v>1.18E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47">
         <v>5000</v>
       </c>
@@ -587,8 +1314,38 @@
       <c r="C47">
         <v>5.9837381893855799</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="D47">
+        <v>13.27389</v>
+      </c>
+      <c r="E47">
+        <v>4.0107299999999997</v>
+      </c>
+      <c r="F47">
+        <v>0.68062</v>
+      </c>
+      <c r="G47">
+        <v>8.7569999999999995E-2</v>
+      </c>
+      <c r="L47">
+        <v>4.7240000000000002</v>
+      </c>
+      <c r="M47">
+        <v>1.2075499999999999</v>
+      </c>
+      <c r="N47">
+        <v>1.1610000000000001E-2</v>
+      </c>
+      <c r="O47">
+        <v>1.9599999999999999E-3</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>8.0300000000000007E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48">
         <v>5050</v>
       </c>
@@ -598,8 +1355,38 @@
       <c r="C48">
         <v>6.3689806914058904</v>
       </c>
-    </row>
-    <row r="49">
+      <c r="D48">
+        <v>11.67825</v>
+      </c>
+      <c r="E48">
+        <v>4.0263999999999998</v>
+      </c>
+      <c r="F48">
+        <v>0.76015999999999995</v>
+      </c>
+      <c r="G48">
+        <v>0.11559</v>
+      </c>
+      <c r="L48">
+        <v>5.7688699999999997</v>
+      </c>
+      <c r="M48">
+        <v>1.79765</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>2.068E-2</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>6.1700000000000001E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49">
         <v>5100</v>
       </c>
@@ -609,8 +1396,32 @@
       <c r="C49">
         <v>7.7656351736133296</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="D49">
+        <v>13.12998</v>
+      </c>
+      <c r="E49">
+        <v>6.2425100000000002</v>
+      </c>
+      <c r="F49">
+        <v>1.0701799999999999</v>
+      </c>
+      <c r="G49">
+        <v>0.13514000000000001</v>
+      </c>
+      <c r="L49">
+        <v>3.3371300000000002</v>
+      </c>
+      <c r="M49">
+        <v>0.95970999999999995</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>4.9300000000000004E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50">
         <v>5150</v>
       </c>
@@ -620,8 +1431,38 @@
       <c r="C50">
         <v>6.0584835318136498</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="D50">
+        <v>10.971310000000001</v>
+      </c>
+      <c r="E50">
+        <v>4.2357399999999998</v>
+      </c>
+      <c r="F50">
+        <v>4.5914099999999998</v>
+      </c>
+      <c r="G50">
+        <v>0.56049000000000004</v>
+      </c>
+      <c r="L50">
+        <v>5.0863100000000001</v>
+      </c>
+      <c r="M50">
+        <v>0.83475999999999995</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>3.5529999999999999E-2</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>2.65E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51">
         <v>5200</v>
       </c>
@@ -631,8 +1472,32 @@
       <c r="C51">
         <v>4.7121427375781098</v>
       </c>
-    </row>
-    <row r="52">
+      <c r="D51">
+        <v>11.598610000000001</v>
+      </c>
+      <c r="E51">
+        <v>2.7954599999999998</v>
+      </c>
+      <c r="F51">
+        <v>2.5047100000000002</v>
+      </c>
+      <c r="G51">
+        <v>0.34808</v>
+      </c>
+      <c r="L51">
+        <v>5.6587399999999999</v>
+      </c>
+      <c r="M51">
+        <v>1.0536000000000001</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>4.6499999999999996E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52">
         <v>5250</v>
       </c>
@@ -642,8 +1507,32 @@
       <c r="C52">
         <v>6.4943237675649499</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="D52">
+        <v>17.439080000000001</v>
+      </c>
+      <c r="E52">
+        <v>2.8374799999999998</v>
+      </c>
+      <c r="F52">
+        <v>1.1567000000000001</v>
+      </c>
+      <c r="G52">
+        <v>0.21429000000000001</v>
+      </c>
+      <c r="L52">
+        <v>4.12913</v>
+      </c>
+      <c r="M52">
+        <v>2.0907100000000001</v>
+      </c>
+      <c r="N52">
+        <v>5.0459999999999998E-2</v>
+      </c>
+      <c r="O52">
+        <v>3.9640000000000002E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53">
         <v>5300</v>
       </c>
@@ -653,8 +1542,38 @@
       <c r="C53">
         <v>4.1816728185405898</v>
       </c>
-    </row>
-    <row r="54">
+      <c r="D53">
+        <v>17.544930000000001</v>
+      </c>
+      <c r="E53">
+        <v>1.50637</v>
+      </c>
+      <c r="F53">
+        <v>2.4226399999999999</v>
+      </c>
+      <c r="G53">
+        <v>0.41424</v>
+      </c>
+      <c r="L53">
+        <v>4.3749399999999996</v>
+      </c>
+      <c r="M53">
+        <v>1.52929</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>1.223E-2</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>7.9382999999999995E-5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54">
         <v>5350</v>
       </c>
@@ -664,8 +1583,44 @@
       <c r="C54">
         <v>3.4183848615052299</v>
       </c>
-    </row>
-    <row r="55">
+      <c r="D54">
+        <v>21.737839999999998</v>
+      </c>
+      <c r="E54">
+        <v>1.0066200000000001</v>
+      </c>
+      <c r="F54">
+        <v>2.4128599999999998</v>
+      </c>
+      <c r="G54">
+        <v>1.03647</v>
+      </c>
+      <c r="H54">
+        <v>3.0880000000000001E-2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>3.6350500000000001</v>
+      </c>
+      <c r="M54">
+        <v>0.96087999999999996</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>8.6499999999999997E-3</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54" s="3">
+        <v>6.8064999999999998E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55">
         <v>5400</v>
       </c>
@@ -675,8 +1630,44 @@
       <c r="C55">
         <v>3.5898698161696898</v>
       </c>
-    </row>
-    <row r="56">
+      <c r="D55">
+        <v>19.352550000000001</v>
+      </c>
+      <c r="E55">
+        <v>1.6369800000000001</v>
+      </c>
+      <c r="F55">
+        <v>1.8428100000000001</v>
+      </c>
+      <c r="G55">
+        <v>0.69303999999999999</v>
+      </c>
+      <c r="H55">
+        <v>2.32E-3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>3.4698600000000002</v>
+      </c>
+      <c r="M55">
+        <v>0.84131</v>
+      </c>
+      <c r="N55">
+        <v>3.7599999999999999E-3</v>
+      </c>
+      <c r="O55">
+        <v>6.2100000000000002E-3</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>1.3500000000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56">
         <v>5450</v>
       </c>
@@ -686,8 +1677,44 @@
       <c r="C56">
         <v>3.1147002088294502</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="D56">
+        <v>20.920649999999998</v>
+      </c>
+      <c r="E56">
+        <v>1.02183</v>
+      </c>
+      <c r="F56">
+        <v>2.24349</v>
+      </c>
+      <c r="G56">
+        <v>0.84697</v>
+      </c>
+      <c r="H56">
+        <v>2E-3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>2.3584100000000001</v>
+      </c>
+      <c r="M56">
+        <v>0.67183000000000004</v>
+      </c>
+      <c r="N56">
+        <v>1.9480000000000001E-2</v>
+      </c>
+      <c r="O56">
+        <v>3.8010000000000002E-2</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56" s="3">
+        <v>4.9885100000000003E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57">
         <v>5500</v>
       </c>
@@ -697,8 +1724,44 @@
       <c r="C57">
         <v>2.7562595407539701</v>
       </c>
-    </row>
-    <row r="58">
+      <c r="D57">
+        <v>16.04823</v>
+      </c>
+      <c r="E57">
+        <v>1.6096200000000001</v>
+      </c>
+      <c r="F57">
+        <v>0.93278000000000005</v>
+      </c>
+      <c r="G57">
+        <v>0.38141000000000003</v>
+      </c>
+      <c r="L57">
+        <v>0.92584999999999995</v>
+      </c>
+      <c r="M57">
+        <v>0.20737</v>
+      </c>
+      <c r="N57">
+        <v>0.13524</v>
+      </c>
+      <c r="O57">
+        <v>0.11642</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>7.4759700000000002E-5</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>6.6256999999999999E-5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58">
         <v>5550</v>
       </c>
@@ -708,8 +1771,44 @@
       <c r="C58">
         <v>2.4179647826033701</v>
       </c>
-    </row>
-    <row r="59">
+      <c r="D58">
+        <v>17.805009999999999</v>
+      </c>
+      <c r="E58">
+        <v>1.4516800000000001</v>
+      </c>
+      <c r="F58">
+        <v>0.78991</v>
+      </c>
+      <c r="G58">
+        <v>0.29298000000000002</v>
+      </c>
+      <c r="L58">
+        <v>0.75268999999999997</v>
+      </c>
+      <c r="M58">
+        <v>2.5489999999999999E-2</v>
+      </c>
+      <c r="N58">
+        <v>2.249E-2</v>
+      </c>
+      <c r="O58">
+        <v>4.4949999999999997E-2</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>6.77E-3</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>6.1806300000000005E-5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59">
         <v>5600</v>
       </c>
@@ -719,8 +1818,44 @@
       <c r="C59">
         <v>3.1169037384601301</v>
       </c>
-    </row>
-    <row r="60">
+      <c r="D59">
+        <v>39.799160000000001</v>
+      </c>
+      <c r="E59">
+        <v>2.0731299999999999</v>
+      </c>
+      <c r="F59">
+        <v>4.3437599999999996</v>
+      </c>
+      <c r="G59">
+        <v>0.45728000000000002</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>1.072E-2</v>
+      </c>
+      <c r="L59">
+        <v>0.4143</v>
+      </c>
+      <c r="M59">
+        <v>1.196E-2</v>
+      </c>
+      <c r="N59">
+        <v>0.10603</v>
+      </c>
+      <c r="O59">
+        <v>8.0699999999999994E-2</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>1.91E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60">
         <v>5650</v>
       </c>
@@ -730,8 +1865,38 @@
       <c r="C60">
         <v>3.4229641520150298</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="D60">
+        <v>24.51502</v>
+      </c>
+      <c r="E60">
+        <v>2.4846699999999999</v>
+      </c>
+      <c r="F60">
+        <v>3.5936400000000002</v>
+      </c>
+      <c r="G60">
+        <v>0.34503</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>9.9192799999999997E-5</v>
+      </c>
+      <c r="N60">
+        <v>0.53519000000000005</v>
+      </c>
+      <c r="O60">
+        <v>8.5370000000000001E-2</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>1.712E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61">
         <v>5700</v>
       </c>
@@ -741,8 +1906,38 @@
       <c r="C61">
         <v>4.0955386147773201</v>
       </c>
-    </row>
-    <row r="62">
+      <c r="D61">
+        <v>33.00244</v>
+      </c>
+      <c r="E61">
+        <v>3.0980400000000001</v>
+      </c>
+      <c r="F61">
+        <v>1.42479</v>
+      </c>
+      <c r="G61">
+        <v>0.29048000000000002</v>
+      </c>
+      <c r="L61">
+        <v>7.2410000000000002E-2</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0.48884</v>
+      </c>
+      <c r="O61">
+        <v>4.1279999999999997E-2</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>4.1489999999999999E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62">
         <v>5750</v>
       </c>
@@ -752,8 +1947,38 @@
       <c r="C62">
         <v>5.1411717584237504</v>
       </c>
-    </row>
-    <row r="63">
+      <c r="D62">
+        <v>35.015749999999997</v>
+      </c>
+      <c r="E62">
+        <v>3.9114399999999998</v>
+      </c>
+      <c r="F62">
+        <v>7.4638400000000003</v>
+      </c>
+      <c r="G62">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="L62">
+        <v>2.1590000000000002E-2</v>
+      </c>
+      <c r="M62">
+        <v>6.8110000000000004E-2</v>
+      </c>
+      <c r="N62">
+        <v>0.15708</v>
+      </c>
+      <c r="O62">
+        <v>6.062E-2</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>9.9739999999999995E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63">
         <v>5800</v>
       </c>
@@ -763,8 +1988,38 @@
       <c r="C63">
         <v>5.5743952029745696</v>
       </c>
-    </row>
-    <row r="64">
+      <c r="D63">
+        <v>43.843649999999997</v>
+      </c>
+      <c r="E63">
+        <v>4.6686699999999997</v>
+      </c>
+      <c r="F63">
+        <v>3.8084799999999999</v>
+      </c>
+      <c r="G63">
+        <v>0.22161</v>
+      </c>
+      <c r="L63">
+        <v>1.7700000000000001E-3</v>
+      </c>
+      <c r="M63">
+        <v>2.6530000000000001E-2</v>
+      </c>
+      <c r="N63">
+        <v>9.7210000000000005E-2</v>
+      </c>
+      <c r="O63">
+        <v>4.539E-2</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>2.7609999999999999E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64">
         <v>5850</v>
       </c>
@@ -774,8 +2029,38 @@
       <c r="C64">
         <v>4.8035887349390496</v>
       </c>
-    </row>
-    <row r="65">
+      <c r="D64">
+        <v>24.904640000000001</v>
+      </c>
+      <c r="E64">
+        <v>2.97723</v>
+      </c>
+      <c r="F64">
+        <v>7.9283799999999998</v>
+      </c>
+      <c r="G64">
+        <v>0.37131999999999998</v>
+      </c>
+      <c r="L64">
+        <v>1.6379999999999999E-2</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0.34944999999999998</v>
+      </c>
+      <c r="O64">
+        <v>2.7959999999999999E-2</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0.94889000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65">
         <v>5900</v>
       </c>
@@ -785,8 +2070,50 @@
       <c r="C65">
         <v>2.2971699500393998</v>
       </c>
-    </row>
-    <row r="66">
+      <c r="D65">
+        <v>12.5913</v>
+      </c>
+      <c r="E65">
+        <v>0.38116</v>
+      </c>
+      <c r="F65">
+        <v>8.1326300000000007</v>
+      </c>
+      <c r="G65">
+        <v>0.57267999999999997</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>5.6600000000000001E-3</v>
+      </c>
+      <c r="L65">
+        <v>1.4120000000000001E-2</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>7.9619999999999996E-2</v>
+      </c>
+      <c r="O65">
+        <v>8.3040000000000003E-2</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0.81664000000000003</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>2.0522699999999998E-6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66">
         <v>5950</v>
       </c>
@@ -796,8 +2123,44 @@
       <c r="C66">
         <v>1.7597124263953701</v>
       </c>
-    </row>
-    <row r="67">
+      <c r="D66">
+        <v>10.44585</v>
+      </c>
+      <c r="E66">
+        <v>0.39045999999999997</v>
+      </c>
+      <c r="F66">
+        <v>7.0626100000000003</v>
+      </c>
+      <c r="G66">
+        <v>0.38517000000000001</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
+        <v>9.7377499999999997E-4</v>
+      </c>
+      <c r="N66">
+        <v>0.49008000000000002</v>
+      </c>
+      <c r="O66">
+        <v>8.0399999999999999E-2</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0.45732</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" s="3">
+        <v>2.9039099999999998E-4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67">
         <v>6000</v>
       </c>
@@ -807,8 +2170,38 @@
       <c r="C67">
         <v>1.8797229534389801</v>
       </c>
-    </row>
-    <row r="68">
+      <c r="D67">
+        <v>13.295109999999999</v>
+      </c>
+      <c r="E67">
+        <v>0.58089000000000002</v>
+      </c>
+      <c r="F67">
+        <v>3.5902500000000002</v>
+      </c>
+      <c r="G67">
+        <v>0.61982000000000004</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>7.43E-3</v>
+      </c>
+      <c r="N67">
+        <v>1.0880300000000001</v>
+      </c>
+      <c r="O67">
+        <v>7.2230000000000003E-2</v>
+      </c>
+      <c r="P67">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q67">
+        <v>0.15432999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68">
         <v>6050</v>
       </c>
@@ -818,8 +2211,38 @@
       <c r="C68">
         <v>1.6324041065775201</v>
       </c>
-    </row>
-    <row r="69">
+      <c r="D68">
+        <v>10.36129</v>
+      </c>
+      <c r="E68">
+        <v>0.58130000000000004</v>
+      </c>
+      <c r="F68">
+        <v>8.2967399999999998</v>
+      </c>
+      <c r="G68">
+        <v>0.50210999999999995</v>
+      </c>
+      <c r="H68">
+        <v>0.14909</v>
+      </c>
+      <c r="I68">
+        <v>2.5190000000000001E-2</v>
+      </c>
+      <c r="N68">
+        <v>0.88914000000000004</v>
+      </c>
+      <c r="O68">
+        <v>0.15504000000000001</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0.14365</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69">
         <v>6100</v>
       </c>
@@ -829,8 +2252,38 @@
       <c r="C69">
         <v>1.5330093731559</v>
       </c>
-    </row>
-    <row r="70">
+      <c r="D69">
+        <v>8.3691300000000002</v>
+      </c>
+      <c r="E69">
+        <v>0.38985999999999998</v>
+      </c>
+      <c r="F69">
+        <v>4.6200999999999999</v>
+      </c>
+      <c r="G69">
+        <v>0.31069999999999998</v>
+      </c>
+      <c r="H69">
+        <v>6.5049999999999997E-2</v>
+      </c>
+      <c r="I69">
+        <v>4.9590000000000002E-2</v>
+      </c>
+      <c r="N69">
+        <v>1.09013</v>
+      </c>
+      <c r="O69">
+        <v>0.12637000000000001</v>
+      </c>
+      <c r="P69">
+        <v>5.7320000000000003E-2</v>
+      </c>
+      <c r="Q69">
+        <v>0.31119000000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70">
         <v>6150</v>
       </c>
@@ -840,8 +2293,38 @@
       <c r="C70">
         <v>2.0444564926943798</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="D70">
+        <v>30.090060000000001</v>
+      </c>
+      <c r="E70">
+        <v>0.55325999999999997</v>
+      </c>
+      <c r="F70">
+        <v>7.5413899999999998</v>
+      </c>
+      <c r="G70">
+        <v>0.28732000000000002</v>
+      </c>
+      <c r="H70">
+        <v>0.22864999999999999</v>
+      </c>
+      <c r="I70">
+        <v>3.8039999999999997E-2</v>
+      </c>
+      <c r="N70">
+        <v>0.86758999999999997</v>
+      </c>
+      <c r="O70">
+        <v>0.21517</v>
+      </c>
+      <c r="P70">
+        <v>0.01</v>
+      </c>
+      <c r="Q70">
+        <v>0.23633999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71">
         <v>6200</v>
       </c>
@@ -851,8 +2334,38 @@
       <c r="C71">
         <v>1.7950992515780499</v>
       </c>
-    </row>
-    <row r="72">
+      <c r="D71">
+        <v>23.705089999999998</v>
+      </c>
+      <c r="E71">
+        <v>0.49221999999999999</v>
+      </c>
+      <c r="F71">
+        <v>5.2307499999999996</v>
+      </c>
+      <c r="G71">
+        <v>0.40366999999999997</v>
+      </c>
+      <c r="H71">
+        <v>0.34443000000000001</v>
+      </c>
+      <c r="I71">
+        <v>6.4700000000000001E-3</v>
+      </c>
+      <c r="N71">
+        <v>2.1120199999999998</v>
+      </c>
+      <c r="O71">
+        <v>0.18101</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>9.0590000000000004E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72">
         <v>6250</v>
       </c>
@@ -862,8 +2375,38 @@
       <c r="C72">
         <v>1.62206947314168</v>
       </c>
-    </row>
-    <row r="73">
+      <c r="D72">
+        <v>5.1166</v>
+      </c>
+      <c r="E72">
+        <v>7.1480000000000002E-2</v>
+      </c>
+      <c r="F72">
+        <v>1.5482100000000001</v>
+      </c>
+      <c r="G72">
+        <v>0.26862000000000003</v>
+      </c>
+      <c r="H72">
+        <v>2.3981400000000002</v>
+      </c>
+      <c r="I72">
+        <v>7.0690000000000003E-2</v>
+      </c>
+      <c r="N72">
+        <v>5.6442199999999998</v>
+      </c>
+      <c r="O72">
+        <v>0.19908999999999999</v>
+      </c>
+      <c r="P72">
+        <v>3.0970000000000001E-2</v>
+      </c>
+      <c r="Q72">
+        <v>0.21909999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73">
         <v>6300</v>
       </c>
@@ -873,8 +2416,38 @@
       <c r="C73">
         <v>1.9015093898420701</v>
       </c>
-    </row>
-    <row r="74">
+      <c r="D73">
+        <v>16.586089999999999</v>
+      </c>
+      <c r="E73">
+        <v>0.13331999999999999</v>
+      </c>
+      <c r="F73">
+        <v>1.77973</v>
+      </c>
+      <c r="G73">
+        <v>0.22325999999999999</v>
+      </c>
+      <c r="H73">
+        <v>3.9152800000000001</v>
+      </c>
+      <c r="I73">
+        <v>9.8479999999999998E-2</v>
+      </c>
+      <c r="N73">
+        <v>4.4274399999999998</v>
+      </c>
+      <c r="O73">
+        <v>0.32401000000000002</v>
+      </c>
+      <c r="P73">
+        <v>0.47119</v>
+      </c>
+      <c r="Q73">
+        <v>0.27721000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74">
         <v>6350</v>
       </c>
@@ -884,8 +2457,44 @@
       <c r="C74">
         <v>1.98983358378259</v>
       </c>
-    </row>
-    <row r="75">
+      <c r="D74">
+        <v>20.652170000000002</v>
+      </c>
+      <c r="E74">
+        <v>4.3209999999999998E-2</v>
+      </c>
+      <c r="F74">
+        <v>3.65205</v>
+      </c>
+      <c r="G74">
+        <v>0.21764</v>
+      </c>
+      <c r="H74">
+        <v>4.1121800000000004</v>
+      </c>
+      <c r="I74">
+        <v>0.28064</v>
+      </c>
+      <c r="N74">
+        <v>7.5449200000000003</v>
+      </c>
+      <c r="O74">
+        <v>0.13214000000000001</v>
+      </c>
+      <c r="P74">
+        <v>0.35244999999999999</v>
+      </c>
+      <c r="Q74">
+        <v>0.17002</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>1.5328E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75">
         <v>6400</v>
       </c>
@@ -895,8 +2504,44 @@
       <c r="C75">
         <v>2.0612282145426</v>
       </c>
-    </row>
-    <row r="76">
+      <c r="D75">
+        <v>11.104240000000001</v>
+      </c>
+      <c r="E75">
+        <v>4.6629999999999998E-2</v>
+      </c>
+      <c r="F75">
+        <v>5.4496599999999997</v>
+      </c>
+      <c r="G75">
+        <v>0.41427999999999998</v>
+      </c>
+      <c r="H75">
+        <v>7.7163300000000001</v>
+      </c>
+      <c r="I75">
+        <v>0.19788</v>
+      </c>
+      <c r="N75">
+        <v>2.7942999999999998</v>
+      </c>
+      <c r="O75">
+        <v>0.10445</v>
+      </c>
+      <c r="P75">
+        <v>0.53149999999999997</v>
+      </c>
+      <c r="Q75">
+        <v>4.9450000000000001E-2</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>2.4399999999999999E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76">
         <v>6450</v>
       </c>
@@ -906,8 +2551,50 @@
       <c r="C76">
         <v>1.62417186817103</v>
       </c>
-    </row>
-    <row r="77">
+      <c r="D76">
+        <v>29.044419999999999</v>
+      </c>
+      <c r="E76">
+        <v>6.762E-2</v>
+      </c>
+      <c r="F76">
+        <v>2.5106799999999998</v>
+      </c>
+      <c r="G76">
+        <v>0.17122999999999999</v>
+      </c>
+      <c r="H76">
+        <v>9.1280699999999992</v>
+      </c>
+      <c r="I76">
+        <v>0.42670000000000002</v>
+      </c>
+      <c r="N76">
+        <v>2.9341200000000001</v>
+      </c>
+      <c r="O76">
+        <v>9.2579999999999996E-2</v>
+      </c>
+      <c r="P76">
+        <v>0.66061000000000003</v>
+      </c>
+      <c r="Q76">
+        <v>5.8880000000000002E-2</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>4.5199999999999997E-3</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76" s="3">
+        <v>5.5995100000000002E-5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77">
         <v>6500</v>
       </c>
@@ -917,8 +2604,50 @@
       <c r="C77">
         <v>1.5300516950101499</v>
       </c>
-    </row>
-    <row r="78">
+      <c r="D77">
+        <v>25.100709999999999</v>
+      </c>
+      <c r="E77">
+        <v>4.7579999999999997E-2</v>
+      </c>
+      <c r="F77">
+        <v>2.7419099999999998</v>
+      </c>
+      <c r="G77">
+        <v>0.15067</v>
+      </c>
+      <c r="H77">
+        <v>10.202870000000001</v>
+      </c>
+      <c r="I77">
+        <v>0.37153000000000003</v>
+      </c>
+      <c r="N77">
+        <v>2.8014100000000002</v>
+      </c>
+      <c r="O77">
+        <v>0.10237</v>
+      </c>
+      <c r="P77">
+        <v>1.62141</v>
+      </c>
+      <c r="Q77">
+        <v>0.153</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>4.2319800000000001E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78">
         <v>6550</v>
       </c>
@@ -928,8 +2657,50 @@
       <c r="C78">
         <v>1.75283102906275</v>
       </c>
-    </row>
-    <row r="79">
+      <c r="D78">
+        <v>18.34421</v>
+      </c>
+      <c r="E78">
+        <v>2.6280000000000001E-2</v>
+      </c>
+      <c r="F78">
+        <v>4.5713200000000001</v>
+      </c>
+      <c r="G78">
+        <v>0.10792</v>
+      </c>
+      <c r="H78">
+        <v>11.03708</v>
+      </c>
+      <c r="I78">
+        <v>0.28037000000000001</v>
+      </c>
+      <c r="N78">
+        <v>0.75260000000000005</v>
+      </c>
+      <c r="O78">
+        <v>0.10706</v>
+      </c>
+      <c r="P78">
+        <v>0.96819</v>
+      </c>
+      <c r="Q78">
+        <v>0.20294000000000001</v>
+      </c>
+      <c r="R78">
+        <v>1.0399999999999999E-3</v>
+      </c>
+      <c r="S78">
+        <v>6.9699999999999996E-3</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78" s="3">
+        <v>3.7939699999999999E-5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79">
         <v>6600</v>
       </c>
@@ -939,8 +2710,44 @@
       <c r="C79">
         <v>1.92035585206318</v>
       </c>
-    </row>
-    <row r="80">
+      <c r="D79">
+        <v>6.9920099999999996</v>
+      </c>
+      <c r="E79">
+        <v>5.6100000000000004E-3</v>
+      </c>
+      <c r="F79">
+        <v>1.1494200000000001</v>
+      </c>
+      <c r="G79">
+        <v>8.2339999999999997E-2</v>
+      </c>
+      <c r="H79">
+        <v>18.855219999999999</v>
+      </c>
+      <c r="I79">
+        <v>0.38306000000000001</v>
+      </c>
+      <c r="N79">
+        <v>4.7503900000000003</v>
+      </c>
+      <c r="O79">
+        <v>0.23374</v>
+      </c>
+      <c r="P79">
+        <v>0.86226999999999998</v>
+      </c>
+      <c r="Q79">
+        <v>0.25541999999999998</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>1.0829999999999999E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80">
         <v>6650</v>
       </c>
@@ -950,8 +2757,50 @@
       <c r="C80">
         <v>2.5378493087271301</v>
       </c>
-    </row>
-    <row r="81">
+      <c r="D80">
+        <v>22.524660000000001</v>
+      </c>
+      <c r="E80">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="F80">
+        <v>0.34443000000000001</v>
+      </c>
+      <c r="G80">
+        <v>0.28626000000000001</v>
+      </c>
+      <c r="H80">
+        <v>12.7638</v>
+      </c>
+      <c r="I80">
+        <v>0.57955000000000001</v>
+      </c>
+      <c r="N80">
+        <v>2.7851599999999999</v>
+      </c>
+      <c r="O80">
+        <v>0.19250999999999999</v>
+      </c>
+      <c r="P80">
+        <v>0.51359999999999995</v>
+      </c>
+      <c r="Q80">
+        <v>0.2145</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>1.8939999999999999E-2</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80" s="3">
+        <v>2.27524E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81">
         <v>6700</v>
       </c>
@@ -961,8 +2810,50 @@
       <c r="C81">
         <v>2.30098690983003</v>
       </c>
-    </row>
-    <row r="82">
+      <c r="D81">
+        <v>32.045870000000001</v>
+      </c>
+      <c r="E81">
+        <v>1.92E-3</v>
+      </c>
+      <c r="F81">
+        <v>1.5428200000000001</v>
+      </c>
+      <c r="G81">
+        <v>0.32893</v>
+      </c>
+      <c r="H81">
+        <v>15.780049999999999</v>
+      </c>
+      <c r="I81">
+        <v>0.56101000000000001</v>
+      </c>
+      <c r="N81">
+        <v>1.98889</v>
+      </c>
+      <c r="O81">
+        <v>8.3979999999999999E-2</v>
+      </c>
+      <c r="P81">
+        <v>2.07463</v>
+      </c>
+      <c r="Q81">
+        <v>0.17086999999999999</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>4.0469999999999999E-2</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82">
         <v>6750</v>
       </c>
@@ -972,8 +2863,44 @@
       <c r="C82">
         <v>2.4060141469469198</v>
       </c>
-    </row>
-    <row r="83">
+      <c r="D82">
+        <v>13.2523</v>
+      </c>
+      <c r="E82" s="3">
+        <v>5.8370299999999998E-4</v>
+      </c>
+      <c r="F82">
+        <v>0.99624999999999997</v>
+      </c>
+      <c r="G82">
+        <v>0.73451999999999995</v>
+      </c>
+      <c r="H82">
+        <v>4.3012499999999996</v>
+      </c>
+      <c r="I82">
+        <v>0.45966000000000001</v>
+      </c>
+      <c r="N82">
+        <v>0.57384000000000002</v>
+      </c>
+      <c r="O82">
+        <v>7.5029999999999999E-2</v>
+      </c>
+      <c r="P82">
+        <v>4.95486</v>
+      </c>
+      <c r="Q82">
+        <v>8.1189999999999998E-2</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>2.9299999999999999E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83">
         <v>6800</v>
       </c>
@@ -983,8 +2910,50 @@
       <c r="C83">
         <v>2.3410251064726699</v>
       </c>
-    </row>
-    <row r="84">
+      <c r="D83">
+        <v>6.5974899999999996</v>
+      </c>
+      <c r="E83">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F83">
+        <v>1.58189</v>
+      </c>
+      <c r="G83">
+        <v>0.62617999999999996</v>
+      </c>
+      <c r="H83">
+        <v>4.8565699999999996</v>
+      </c>
+      <c r="I83">
+        <v>0.32078000000000001</v>
+      </c>
+      <c r="N83">
+        <v>0.66066000000000003</v>
+      </c>
+      <c r="O83">
+        <v>0.17419000000000001</v>
+      </c>
+      <c r="P83">
+        <v>2.54467</v>
+      </c>
+      <c r="Q83">
+        <v>3.8330000000000003E-2</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>2.3500000000000001E-3</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>1.28128E-4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84">
         <v>6850</v>
       </c>
@@ -994,8 +2963,50 @@
       <c r="C84">
         <v>2.8673838399381899</v>
       </c>
-    </row>
-    <row r="85">
+      <c r="D84">
+        <v>9.4637499999999992</v>
+      </c>
+      <c r="E84" s="3">
+        <v>9.1201200000000002E-4</v>
+      </c>
+      <c r="F84">
+        <v>2.23001</v>
+      </c>
+      <c r="G84">
+        <v>0.67957999999999996</v>
+      </c>
+      <c r="H84">
+        <v>4.6393500000000003</v>
+      </c>
+      <c r="I84">
+        <v>0.37930000000000003</v>
+      </c>
+      <c r="N84">
+        <v>0.16309999999999999</v>
+      </c>
+      <c r="O84">
+        <v>9.0429999999999996E-2</v>
+      </c>
+      <c r="P84">
+        <v>4.5780399999999997</v>
+      </c>
+      <c r="Q84">
+        <v>5.7389999999999997E-2</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>2.0789999999999999E-2</v>
+      </c>
+      <c r="T84">
+        <v>1.353E-2</v>
+      </c>
+      <c r="U84">
+        <v>1.8799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85">
         <v>6900</v>
       </c>
@@ -1005,8 +3016,50 @@
       <c r="C85">
         <v>1.80594868487073</v>
       </c>
-    </row>
-    <row r="86">
+      <c r="D85">
+        <v>1.6553500000000001</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>1.9541599999999999</v>
+      </c>
+      <c r="G85">
+        <v>0.44007000000000002</v>
+      </c>
+      <c r="H85">
+        <v>9.1640200000000007</v>
+      </c>
+      <c r="I85">
+        <v>0.23266000000000001</v>
+      </c>
+      <c r="N85">
+        <v>0.87704000000000004</v>
+      </c>
+      <c r="O85">
+        <v>3.0300000000000001E-3</v>
+      </c>
+      <c r="P85">
+        <v>11.234769999999999</v>
+      </c>
+      <c r="Q85">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>1.461E-2</v>
+      </c>
+      <c r="T85">
+        <v>4.4099999999999999E-3</v>
+      </c>
+      <c r="U85">
+        <v>4.1099999999999999E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86">
         <v>6950</v>
       </c>
@@ -1016,8 +3069,50 @@
       <c r="C86">
         <v>1.0955514259153201</v>
       </c>
-    </row>
-    <row r="87">
+      <c r="D86">
+        <v>1.0335099999999999</v>
+      </c>
+      <c r="E86" s="3">
+        <v>1.8345299999999999E-5</v>
+      </c>
+      <c r="F86">
+        <v>1.1936199999999999</v>
+      </c>
+      <c r="G86">
+        <v>0.27629999999999999</v>
+      </c>
+      <c r="H86">
+        <v>4.1657400000000004</v>
+      </c>
+      <c r="I86">
+        <v>6.2469999999999998E-2</v>
+      </c>
+      <c r="N86">
+        <v>9.4229999999999994E-2</v>
+      </c>
+      <c r="O86">
+        <v>5.2130000000000003E-2</v>
+      </c>
+      <c r="P86">
+        <v>1.4793499999999999</v>
+      </c>
+      <c r="Q86">
+        <v>2.1610000000000001E-2</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>9.6399999999999993E-3</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86">
+        <v>3.46E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87">
         <v>7000</v>
       </c>
@@ -1027,8 +3122,50 @@
       <c r="C87">
         <v>0.84659681815797405</v>
       </c>
-    </row>
-    <row r="88">
+      <c r="D87">
+        <v>1.8243400000000001</v>
+      </c>
+      <c r="E87" s="3">
+        <v>5.7628499999999995E-4</v>
+      </c>
+      <c r="F87">
+        <v>2.13123</v>
+      </c>
+      <c r="G87">
+        <v>0.29743999999999998</v>
+      </c>
+      <c r="H87">
+        <v>1.05904</v>
+      </c>
+      <c r="I87">
+        <v>6.4599999999999996E-3</v>
+      </c>
+      <c r="N87">
+        <v>1.6570000000000001E-2</v>
+      </c>
+      <c r="O87">
+        <v>1.307E-2</v>
+      </c>
+      <c r="P87">
+        <v>2.70174</v>
+      </c>
+      <c r="Q87">
+        <v>3.1820000000000001E-2</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="T87">
+        <v>0.13494999999999999</v>
+      </c>
+      <c r="U87" s="3">
+        <v>2.6874000000000001E-5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88">
         <v>7050</v>
       </c>
@@ -1038,8 +3175,44 @@
       <c r="C88">
         <v>0.63493213400138404</v>
       </c>
-    </row>
-    <row r="89">
+      <c r="D88">
+        <v>6.7107200000000002</v>
+      </c>
+      <c r="E88">
+        <v>8.4499999999999992E-3</v>
+      </c>
+      <c r="F88">
+        <v>2.00231</v>
+      </c>
+      <c r="G88">
+        <v>6.3259999999999997E-2</v>
+      </c>
+      <c r="H88">
+        <v>3.1477599999999999</v>
+      </c>
+      <c r="I88">
+        <v>5.1679999999999997E-2</v>
+      </c>
+      <c r="P88">
+        <v>0.52154</v>
+      </c>
+      <c r="Q88">
+        <v>3.6099999999999999E-3</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>3.2439999999999997E-2</v>
+      </c>
+      <c r="T88">
+        <v>2.8219999999999999E-2</v>
+      </c>
+      <c r="U88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89">
         <v>7100</v>
       </c>
@@ -1049,8 +3222,44 @@
       <c r="C89">
         <v>1.0441232637237401</v>
       </c>
-    </row>
-    <row r="90">
+      <c r="D89">
+        <v>2.21414</v>
+      </c>
+      <c r="E89">
+        <v>1.1129999999999999E-2</v>
+      </c>
+      <c r="F89">
+        <v>2.9536500000000001</v>
+      </c>
+      <c r="G89">
+        <v>0.13733999999999999</v>
+      </c>
+      <c r="H89">
+        <v>6.5702299999999996</v>
+      </c>
+      <c r="I89">
+        <v>5.425E-2</v>
+      </c>
+      <c r="P89">
+        <v>0.30336000000000002</v>
+      </c>
+      <c r="Q89">
+        <v>2.052E-2</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>1.184E-2</v>
+      </c>
+      <c r="T89">
+        <v>0.18123</v>
+      </c>
+      <c r="U89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90">
         <v>7150</v>
       </c>
@@ -1060,8 +3269,44 @@
       <c r="C90">
         <v>1.5307682625427399</v>
       </c>
-    </row>
-    <row r="91">
+      <c r="D90">
+        <v>2.3511199999999999</v>
+      </c>
+      <c r="E90">
+        <v>2.2899999999999999E-3</v>
+      </c>
+      <c r="F90">
+        <v>1.1642999999999999</v>
+      </c>
+      <c r="G90">
+        <v>0.35193999999999998</v>
+      </c>
+      <c r="H90">
+        <v>2.7972000000000001</v>
+      </c>
+      <c r="I90">
+        <v>1.6760000000000001E-2</v>
+      </c>
+      <c r="P90">
+        <v>0.36187999999999998</v>
+      </c>
+      <c r="Q90">
+        <v>9.2630000000000004E-2</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>9.4369999999999996E-2</v>
+      </c>
+      <c r="T90">
+        <v>0.87502000000000002</v>
+      </c>
+      <c r="U90">
+        <v>4.0899999999999999E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91">
         <v>7200</v>
       </c>
@@ -1071,8 +3316,44 @@
       <c r="C91">
         <v>1.43302262336654</v>
       </c>
-    </row>
-    <row r="92">
+      <c r="D91">
+        <v>6.5413800000000002</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>6.3643299999999998</v>
+      </c>
+      <c r="G91">
+        <v>0.81486999999999998</v>
+      </c>
+      <c r="H91">
+        <v>3.7885</v>
+      </c>
+      <c r="I91">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="P91">
+        <v>0.55405000000000004</v>
+      </c>
+      <c r="Q91">
+        <v>0.14432</v>
+      </c>
+      <c r="R91">
+        <v>6.4599999999999996E-3</v>
+      </c>
+      <c r="S91">
+        <v>2.9329999999999998E-2</v>
+      </c>
+      <c r="T91">
+        <v>0.52856000000000003</v>
+      </c>
+      <c r="U91">
+        <v>4.2399999999999998E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92">
         <v>7250</v>
       </c>
@@ -1082,8 +3363,44 @@
       <c r="C92">
         <v>0.99111215083715698</v>
       </c>
-    </row>
-    <row r="93">
+      <c r="D92">
+        <v>15.75914</v>
+      </c>
+      <c r="E92">
+        <v>1.1979999999999999E-2</v>
+      </c>
+      <c r="F92">
+        <v>6.3384400000000003</v>
+      </c>
+      <c r="G92">
+        <v>0.49823000000000001</v>
+      </c>
+      <c r="H92">
+        <v>8.5926899999999993</v>
+      </c>
+      <c r="I92">
+        <v>1.2290000000000001E-2</v>
+      </c>
+      <c r="P92">
+        <v>7.5100000000000002E-3</v>
+      </c>
+      <c r="Q92">
+        <v>8.2809999999999995E-2</v>
+      </c>
+      <c r="R92">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="S92">
+        <v>0.22839999999999999</v>
+      </c>
+      <c r="T92">
+        <v>0.24945000000000001</v>
+      </c>
+      <c r="U92" s="3">
+        <v>4.96935E-4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93">
         <v>7300</v>
       </c>
@@ -1093,8 +3410,44 @@
       <c r="C93">
         <v>2.0242673573004</v>
       </c>
-    </row>
-    <row r="94">
+      <c r="D93">
+        <v>0.23196</v>
+      </c>
+      <c r="E93" s="3">
+        <v>8.7379700000000005E-4</v>
+      </c>
+      <c r="F93">
+        <v>21.076049999999999</v>
+      </c>
+      <c r="G93">
+        <v>1.23637</v>
+      </c>
+      <c r="H93">
+        <v>9.1103400000000008</v>
+      </c>
+      <c r="I93" s="3">
+        <v>1.5816900000000001E-5</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>6.5530000000000005E-2</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <v>0.16671</v>
+      </c>
+      <c r="T93">
+        <v>0.29493000000000003</v>
+      </c>
+      <c r="U93">
+        <v>6.6600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94">
         <v>7350</v>
       </c>
@@ -1104,8 +3457,44 @@
       <c r="C94">
         <v>1.75615026295181</v>
       </c>
-    </row>
-    <row r="95">
+      <c r="D94">
+        <v>0.31228</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>9.2039000000000009</v>
+      </c>
+      <c r="G94">
+        <v>1.2614099999999999</v>
+      </c>
+      <c r="H94">
+        <v>50.901060000000001</v>
+      </c>
+      <c r="I94" s="3">
+        <v>1.3667599999999999E-5</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>1.87121E-5</v>
+      </c>
+      <c r="R94">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="S94">
+        <v>7.46E-2</v>
+      </c>
+      <c r="T94">
+        <v>0.26322000000000001</v>
+      </c>
+      <c r="U94" s="3">
+        <v>2.1433100000000001E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95">
         <v>7400</v>
       </c>
@@ -1115,8 +3504,50 @@
       <c r="C95">
         <v>1.33761235396863</v>
       </c>
-    </row>
-    <row r="96">
+      <c r="D95">
+        <v>0.97902999999999996</v>
+      </c>
+      <c r="E95">
+        <v>1.32E-3</v>
+      </c>
+      <c r="F95">
+        <v>3.39655</v>
+      </c>
+      <c r="G95">
+        <v>0.88892000000000004</v>
+      </c>
+      <c r="H95">
+        <v>2.9680800000000001</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>2.64E-3</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0.63710999999999995</v>
+      </c>
+      <c r="Q95">
+        <v>3.6940000000000001E-2</v>
+      </c>
+      <c r="R95">
+        <v>1.4279999999999999E-2</v>
+      </c>
+      <c r="S95">
+        <v>0.11082</v>
+      </c>
+      <c r="T95">
+        <v>0.14074</v>
+      </c>
+      <c r="U95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96">
         <v>7450</v>
       </c>
@@ -1126,8 +3557,50 @@
       <c r="C96">
         <v>0.95165278953259103</v>
       </c>
-    </row>
-    <row r="97">
+      <c r="D96">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2.1528499999999999E-5</v>
+      </c>
+      <c r="F96">
+        <v>21.518940000000001</v>
+      </c>
+      <c r="G96">
+        <v>0.32</v>
+      </c>
+      <c r="H96">
+        <v>9.2240000000000003E-2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0.11946</v>
+      </c>
+      <c r="Q96">
+        <v>1.0319999999999999E-2</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <v>2.102E-2</v>
+      </c>
+      <c r="T96">
+        <v>0.14097000000000001</v>
+      </c>
+      <c r="U96" s="3">
+        <v>2.57805E-4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97">
         <v>7500</v>
       </c>
@@ -1137,8 +3610,38 @@
       <c r="C97">
         <v>1.7270275843624101</v>
       </c>
-    </row>
-    <row r="98">
+      <c r="D97">
+        <v>0.42712</v>
+      </c>
+      <c r="E97">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="F97">
+        <v>7.8605999999999998</v>
+      </c>
+      <c r="G97">
+        <v>0.15653</v>
+      </c>
+      <c r="P97">
+        <v>1.7270000000000001E-2</v>
+      </c>
+      <c r="Q97">
+        <v>2.5409999999999999E-2</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>1.222E-2</v>
+      </c>
+      <c r="T97">
+        <v>5.8319999999999997E-2</v>
+      </c>
+      <c r="U97">
+        <v>2.6900000000000001E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98">
         <v>7550</v>
       </c>
@@ -1148,8 +3651,44 @@
       <c r="C98">
         <v>0.55907957608369396</v>
       </c>
-    </row>
-    <row r="99">
+      <c r="D98">
+        <v>0.48734</v>
+      </c>
+      <c r="E98" s="3">
+        <v>8.8831899999999999E-5</v>
+      </c>
+      <c r="F98">
+        <v>5.7637099999999997</v>
+      </c>
+      <c r="G98">
+        <v>0.12406</v>
+      </c>
+      <c r="N98">
+        <v>7.3699999999999998E-3</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>3.075E-2</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>9.3867699999999996E-4</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <v>2.1409999999999998E-2</v>
+      </c>
+      <c r="T98">
+        <v>0.24015</v>
+      </c>
+      <c r="U98">
+        <v>2.9989999999999999E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99">
         <v>7600</v>
       </c>
@@ -1159,8 +3698,44 @@
       <c r="C99">
         <v>0.53511375498120906</v>
       </c>
-    </row>
-    <row r="100">
+      <c r="D99">
+        <v>0.31184000000000001</v>
+      </c>
+      <c r="E99">
+        <v>4.8700000000000002E-3</v>
+      </c>
+      <c r="F99">
+        <v>4.6628400000000001</v>
+      </c>
+      <c r="G99">
+        <v>0.10879</v>
+      </c>
+      <c r="N99">
+        <v>0.12307999999999999</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>8.7823299999999997E-4</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99">
+        <v>2.2360000000000001E-2</v>
+      </c>
+      <c r="T99">
+        <v>0.33983000000000002</v>
+      </c>
+      <c r="U99">
+        <v>2.5489999999999999E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100">
         <v>7650</v>
       </c>
@@ -1170,8 +3745,44 @@
       <c r="C100">
         <v>0.52976177657357004</v>
       </c>
-    </row>
-    <row r="101">
+      <c r="D100">
+        <v>0.60419</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6.7917800000000001E-4</v>
+      </c>
+      <c r="F100">
+        <v>13.13618</v>
+      </c>
+      <c r="G100">
+        <v>0.16408</v>
+      </c>
+      <c r="N100">
+        <v>5.2260000000000001E-2</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0.26471</v>
+      </c>
+      <c r="Q100">
+        <v>5.9500000000000004E-3</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100">
+        <v>2.291E-2</v>
+      </c>
+      <c r="T100">
+        <v>0.67647999999999997</v>
+      </c>
+      <c r="U100">
+        <v>8.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101">
         <v>7700</v>
       </c>
@@ -1181,8 +3792,38 @@
       <c r="C101">
         <v>0.75414953288338504</v>
       </c>
-    </row>
-    <row r="102">
+      <c r="D101">
+        <v>0.50007999999999997</v>
+      </c>
+      <c r="E101">
+        <v>1.4E-3</v>
+      </c>
+      <c r="F101">
+        <v>11.28246</v>
+      </c>
+      <c r="G101">
+        <v>0.60611000000000004</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>2.528E-2</v>
+      </c>
+      <c r="R101">
+        <v>0.16603999999999999</v>
+      </c>
+      <c r="S101">
+        <v>7.9500000000000005E-3</v>
+      </c>
+      <c r="T101">
+        <v>0.53947000000000001</v>
+      </c>
+      <c r="U101" s="3">
+        <v>3.8662000000000001E-4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102">
         <v>7750</v>
       </c>
@@ -1192,8 +3833,44 @@
       <c r="C102">
         <v>0.893890751031307</v>
       </c>
-    </row>
-    <row r="103">
+      <c r="D102">
+        <v>0.73646</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>20.723400000000002</v>
+      </c>
+      <c r="G102">
+        <v>0.57216</v>
+      </c>
+      <c r="N102">
+        <v>8.0599999999999995E-3</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0.20707</v>
+      </c>
+      <c r="Q102">
+        <v>0</v>
+      </c>
+      <c r="R102">
+        <v>1.65594</v>
+      </c>
+      <c r="S102">
+        <v>0.11613999999999999</v>
+      </c>
+      <c r="T102">
+        <v>3.0759999999999999E-2</v>
+      </c>
+      <c r="U102" s="3">
+        <v>5.2259400000000003E-4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103">
         <v>7800</v>
       </c>
@@ -1203,8 +3880,38 @@
       <c r="C103">
         <v>0.529610969774157</v>
       </c>
-    </row>
-    <row r="104">
+      <c r="D103">
+        <v>0.43567</v>
+      </c>
+      <c r="E103">
+        <v>4.8399999999999997E-3</v>
+      </c>
+      <c r="F103">
+        <v>13.3431</v>
+      </c>
+      <c r="G103">
+        <v>0.30909999999999999</v>
+      </c>
+      <c r="P103" s="3">
+        <v>6.4008999999999995E-4</v>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="R103">
+        <v>1.8035699999999999</v>
+      </c>
+      <c r="S103">
+        <v>4.777E-2</v>
+      </c>
+      <c r="T103">
+        <v>3.3340000000000002E-2</v>
+      </c>
+      <c r="U103" s="3">
+        <v>5.3162499999999998E-5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104">
         <v>7850</v>
       </c>
@@ -1214,8 +3921,32 @@
       <c r="C104">
         <v>0.48813572057757798</v>
       </c>
-    </row>
-    <row r="105">
+      <c r="D104">
+        <v>0.28806999999999999</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>10.43984</v>
+      </c>
+      <c r="G104">
+        <v>0.17724000000000001</v>
+      </c>
+      <c r="R104">
+        <v>1.3496600000000001</v>
+      </c>
+      <c r="S104">
+        <v>7.034E-2</v>
+      </c>
+      <c r="T104">
+        <v>2.4109999999999999E-2</v>
+      </c>
+      <c r="U104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105">
         <v>7900</v>
       </c>
@@ -1225,8 +3956,32 @@
       <c r="C105">
         <v>0.31463358749250803</v>
       </c>
-    </row>
-    <row r="106">
+      <c r="D105">
+        <v>5.6959999999999997E-2</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>5.1695399999999996</v>
+      </c>
+      <c r="G105">
+        <v>0.15404000000000001</v>
+      </c>
+      <c r="R105">
+        <v>0.42320000000000002</v>
+      </c>
+      <c r="S105">
+        <v>4.5879999999999997E-2</v>
+      </c>
+      <c r="T105">
+        <v>0.53125</v>
+      </c>
+      <c r="U105" s="3">
+        <v>3.83218E-4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106">
         <v>7950</v>
       </c>
@@ -1236,8 +3991,32 @@
       <c r="C106">
         <v>0.33314968707824</v>
       </c>
-    </row>
-    <row r="107">
+      <c r="D106">
+        <v>5.568E-2</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>35.059930000000001</v>
+      </c>
+      <c r="G106">
+        <v>3.7269999999999998E-2</v>
+      </c>
+      <c r="R106">
+        <v>2.1930900000000002</v>
+      </c>
+      <c r="S106">
+        <v>0.16596</v>
+      </c>
+      <c r="T106">
+        <v>1.983E-2</v>
+      </c>
+      <c r="U106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107">
         <v>8000</v>
       </c>
@@ -1247,8 +4026,32 @@
       <c r="C107">
         <v>0.40095389193335301</v>
       </c>
-    </row>
-    <row r="108">
+      <c r="D107">
+        <v>2.7279999999999999E-2</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>2.4595500000000001</v>
+      </c>
+      <c r="G107">
+        <v>0.10199</v>
+      </c>
+      <c r="R107">
+        <v>4.2714400000000001</v>
+      </c>
+      <c r="S107">
+        <v>0.20243</v>
+      </c>
+      <c r="T107">
+        <v>2.2239999999999999E-2</v>
+      </c>
+      <c r="U107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108">
         <v>8050</v>
       </c>
@@ -1258,8 +4061,26 @@
       <c r="C108">
         <v>0.25834880467329802</v>
       </c>
-    </row>
-    <row r="109">
+      <c r="F108">
+        <v>1.40855</v>
+      </c>
+      <c r="G108">
+        <v>1.17E-3</v>
+      </c>
+      <c r="R108">
+        <v>6.2668999999999997</v>
+      </c>
+      <c r="S108">
+        <v>0.14768999999999999</v>
+      </c>
+      <c r="T108">
+        <v>0.11959</v>
+      </c>
+      <c r="U108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109">
         <v>8100</v>
       </c>
@@ -1269,8 +4090,20 @@
       <c r="C109">
         <v>0.26906339197784901</v>
       </c>
-    </row>
-    <row r="110">
+      <c r="R109">
+        <v>5.3119100000000001</v>
+      </c>
+      <c r="S109">
+        <v>0.12194000000000001</v>
+      </c>
+      <c r="T109">
+        <v>0.18134</v>
+      </c>
+      <c r="U109" s="3">
+        <v>9.3543500000000003E-5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21">
       <c r="A110">
         <v>8150</v>
       </c>
@@ -1278,10 +4111,22 @@
         <v>7.8229680800559498</v>
       </c>
       <c r="C110">
-        <v>0.095071004532059605</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>9.5071004532059605E-2</v>
+      </c>
+      <c r="R110">
+        <v>3.09158</v>
+      </c>
+      <c r="S110">
+        <v>5.4760000000000003E-2</v>
+      </c>
+      <c r="T110">
+        <v>7.7469999999999997E-2</v>
+      </c>
+      <c r="U110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21">
       <c r="A111">
         <v>8200</v>
       </c>
@@ -1289,10 +4134,28 @@
         <v>8.0685985656197996</v>
       </c>
       <c r="C111">
-        <v>0.045000047720040903</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>4.5000047720040903E-2</v>
+      </c>
+      <c r="H111" s="3">
+        <v>3.19716E-4</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="R111">
+        <v>4.3567499999999999</v>
+      </c>
+      <c r="S111">
+        <v>2.6110000000000001E-2</v>
+      </c>
+      <c r="T111">
+        <v>6.8799999999999998E-3</v>
+      </c>
+      <c r="U111">
+        <v>1.65E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21">
       <c r="A112">
         <v>8250</v>
       </c>
@@ -1300,10 +4163,28 @@
         <v>10.816134461012201</v>
       </c>
       <c r="C112">
-        <v>0.020692956387879401</v>
-      </c>
-    </row>
-    <row r="113">
+        <v>2.0692956387879401E-2</v>
+      </c>
+      <c r="D112">
+        <v>0.50461999999999996</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="R112">
+        <v>9.5750799999999998</v>
+      </c>
+      <c r="S112">
+        <v>3.0100000000000001E-3</v>
+      </c>
+      <c r="T112">
+        <v>1.7600000000000001E-3</v>
+      </c>
+      <c r="U112" s="3">
+        <v>2.0428699999999999E-4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21">
       <c r="A113">
         <v>8300</v>
       </c>
@@ -1311,10 +4192,40 @@
         <v>2.8010816930207501</v>
       </c>
       <c r="C113">
-        <v>0.0085047653448131096</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>8.5047653448131096E-3</v>
+      </c>
+      <c r="D113">
+        <v>3.9199999999999999E-3</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="H113" s="3">
+        <v>8.7992500000000004E-4</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>7.6899999999999998E-3</v>
+      </c>
+      <c r="Q113">
+        <v>0</v>
+      </c>
+      <c r="R113">
+        <v>0.13186</v>
+      </c>
+      <c r="S113">
+        <v>4.0499999999999998E-3</v>
+      </c>
+      <c r="T113">
+        <v>0.47189999999999999</v>
+      </c>
+      <c r="U113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21">
       <c r="A114">
         <v>8350</v>
       </c>
@@ -1324,8 +4235,20 @@
       <c r="C114">
         <v>0.58222468679552997</v>
       </c>
-    </row>
-    <row r="115">
+      <c r="R114">
+        <v>0</v>
+      </c>
+      <c r="S114" s="3">
+        <v>4.3105200000000002E-4</v>
+      </c>
+      <c r="T114">
+        <v>0.81925000000000003</v>
+      </c>
+      <c r="U114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21">
       <c r="A115">
         <v>8400</v>
       </c>
@@ -1333,10 +4256,16 @@
         <v>0.24674671559445699</v>
       </c>
       <c r="C115">
-        <v>0.0122928540721376</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>1.22928540721376E-2</v>
+      </c>
+      <c r="R115">
+        <v>0.21174000000000001</v>
+      </c>
+      <c r="S115">
+        <v>6.7299999999999999E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21">
       <c r="A116">
         <v>8450</v>
       </c>
@@ -1344,10 +4273,16 @@
         <v>5.88293088606257</v>
       </c>
       <c r="C116">
-        <v>0.0047391950116491503</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>4.7391950116491503E-3</v>
+      </c>
+      <c r="R116">
+        <v>0</v>
+      </c>
+      <c r="S116" s="3">
+        <v>2.6966199999999999E-6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21">
       <c r="A117">
         <v>8500</v>
       </c>
@@ -1355,10 +4290,16 @@
         <v>10.3618035234941</v>
       </c>
       <c r="C117">
-        <v>0.030875163789571999</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>3.0875163789571999E-2</v>
+      </c>
+      <c r="T117">
+        <v>0.34520000000000001</v>
+      </c>
+      <c r="U117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
       <c r="A118">
         <v>8550</v>
       </c>
@@ -1366,10 +4307,16 @@
         <v>4.9972099810545796</v>
       </c>
       <c r="C118">
-        <v>0.0161185155294369</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>1.61185155294369E-2</v>
+      </c>
+      <c r="T118">
+        <v>0.35104999999999997</v>
+      </c>
+      <c r="U118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
       <c r="A119">
         <v>8600</v>
       </c>
@@ -1377,10 +4324,16 @@
         <v>0.120663265903014</v>
       </c>
       <c r="C119">
-        <v>0.00055615336306122202</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>5.5615336306122202E-4</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119" s="3">
+        <v>4.7075399999999999E-4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21">
       <c r="A120">
         <v>8650</v>
       </c>
@@ -1391,29 +4344,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:21">
       <c r="A121">
         <v>8700</v>
       </c>
       <c r="B121">
-        <v>0.00032020006295454802</v>
+        <v>3.2020006295454802E-4</v>
       </c>
       <c r="C121">
-        <v>0.00031570999376287799</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>3.1570999376287799E-4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21">
       <c r="A122">
         <v>8750</v>
       </c>
       <c r="B122">
-        <v>0.017199654943499398</v>
+        <v>1.7199654943499398E-2</v>
       </c>
       <c r="C122">
-        <v>0.00052286539769259399</v>
-      </c>
-    </row>
-    <row r="123">
+        <v>5.2286539769259399E-4</v>
+      </c>
+      <c r="T122">
+        <v>5.8399999999999997E-3</v>
+      </c>
+      <c r="U122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21">
       <c r="A123">
         <v>8800</v>
       </c>
@@ -1421,10 +4380,16 @@
         <v>0.24970679485867101</v>
       </c>
       <c r="C123">
-        <v>0.00203012669316499</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>2.03012669316499E-3</v>
+      </c>
+      <c r="T123">
+        <v>0.23488999999999999</v>
+      </c>
+      <c r="U123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21">
       <c r="A124">
         <v>8850</v>
       </c>
@@ -1432,21 +4397,33 @@
         <v>1.68946129296993</v>
       </c>
       <c r="C124">
-        <v>0.00023086808035797899</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>2.3086808035797899E-4</v>
+      </c>
+      <c r="T124">
+        <v>1.6148199999999999</v>
+      </c>
+      <c r="U124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21">
       <c r="A125">
         <v>8900</v>
       </c>
       <c r="B125">
-        <v>0.043972089619375897</v>
+        <v>4.3972089619375897E-2</v>
       </c>
       <c r="C125">
-        <v>0.0099662723883079708</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>9.9662723883079708E-3</v>
+      </c>
+      <c r="T125">
+        <v>4.3970000000000002E-2</v>
+      </c>
+      <c r="U125">
+        <v>9.2599999999999991E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
       <c r="A126">
         <v>8950</v>
       </c>
@@ -1454,10 +4431,16 @@
         <v>0.27188117460029398</v>
       </c>
       <c r="C126">
-        <v>0.0016337542090184699</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>1.6337542090184699E-3</v>
+      </c>
+      <c r="T126">
+        <v>0.11788</v>
+      </c>
+      <c r="U126">
+        <v>1.0200000000000001E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21">
       <c r="A127">
         <v>9000</v>
       </c>
@@ -1467,8 +4450,14 @@
       <c r="C127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128">
+      <c r="T127">
+        <v>0.55861000000000005</v>
+      </c>
+      <c r="U127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21">
       <c r="A128">
         <v>9050</v>
       </c>
@@ -1476,10 +4465,16 @@
         <v>0.45645534759227002</v>
       </c>
       <c r="C128">
-        <v>0.0047197687624360198</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>4.7197687624360198E-3</v>
+      </c>
+      <c r="T128">
+        <v>0.45645999999999998</v>
+      </c>
+      <c r="U128">
+        <v>4.7200000000000002E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21">
       <c r="A129">
         <v>9100</v>
       </c>
@@ -1487,10 +4482,16 @@
         <v>3.69646634279685</v>
       </c>
       <c r="C129">
-        <v>0.0022852213020399998</v>
-      </c>
-    </row>
-    <row r="130">
+        <v>2.2852213020399998E-3</v>
+      </c>
+      <c r="T129">
+        <v>3.6964700000000001</v>
+      </c>
+      <c r="U129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21">
       <c r="A130">
         <v>9150</v>
       </c>
@@ -1500,8 +4501,14 @@
       <c r="C130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131">
+      <c r="T130">
+        <v>6.7988</v>
+      </c>
+      <c r="U130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21">
       <c r="A131">
         <v>9200</v>
       </c>
@@ -1511,8 +4518,14 @@
       <c r="C131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132">
+      <c r="T131">
+        <v>0.24367</v>
+      </c>
+      <c r="U131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21">
       <c r="A132">
         <v>9250</v>
       </c>
@@ -1520,10 +4533,16 @@
         <v>0.237309649891496</v>
       </c>
       <c r="C132">
-        <v>0.00075875245112891798</v>
-      </c>
-    </row>
-    <row r="133">
+        <v>7.5875245112891798E-4</v>
+      </c>
+      <c r="T132">
+        <v>0.23730999999999999</v>
+      </c>
+      <c r="U132" s="3">
+        <v>7.5875200000000002E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21">
       <c r="A133">
         <v>9300</v>
       </c>
@@ -1531,10 +4550,16 @@
         <v>0</v>
       </c>
       <c r="C133">
-        <v>0.00018106023848041901</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>1.8106023848041901E-4</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133" s="3">
+        <v>1.8106E-4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21">
       <c r="A134">
         <v>9350</v>
       </c>
@@ -1542,10 +4567,16 @@
         <v>2.0058517222994601</v>
       </c>
       <c r="C134">
-        <v>0.000239473045740562</v>
-      </c>
-    </row>
-    <row r="135">
+        <v>2.39473045740562E-4</v>
+      </c>
+      <c r="T134">
+        <v>1.85083</v>
+      </c>
+      <c r="U134" s="3">
+        <v>2.39473E-4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21">
       <c r="A135">
         <v>9400</v>
       </c>
@@ -1553,10 +4584,16 @@
         <v>1.37791987714591</v>
       </c>
       <c r="C135">
-        <v>0.00025898142796821</v>
-      </c>
-    </row>
-    <row r="136">
+        <v>2.5898142796821E-4</v>
+      </c>
+      <c r="T135">
+        <v>1.2216199999999999</v>
+      </c>
+      <c r="U135" s="3">
+        <v>6.40167E-5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21">
       <c r="A136">
         <v>9450</v>
       </c>
@@ -1566,8 +4603,14 @@
       <c r="C136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137">
+      <c r="T136">
+        <v>0.33571000000000001</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21">
       <c r="A137">
         <v>9500</v>
       </c>
@@ -1577,8 +4620,14 @@
       <c r="C137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138">
+      <c r="T137">
+        <v>0.84286000000000005</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21">
       <c r="A138">
         <v>9550</v>
       </c>
@@ -1586,10 +4635,16 @@
         <v>7.1187283855865102</v>
       </c>
       <c r="C138">
-        <v>0.0011239152475922499</v>
-      </c>
-    </row>
-    <row r="139">
+        <v>1.1239152475922499E-3</v>
+      </c>
+      <c r="T138">
+        <v>7.1187300000000002</v>
+      </c>
+      <c r="U138">
+        <v>1.1199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21">
       <c r="A139">
         <v>9600</v>
       </c>
@@ -1599,8 +4654,14 @@
       <c r="C139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140">
+      <c r="T139">
+        <v>1.788E-2</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21">
       <c r="A140">
         <v>9650</v>
       </c>
@@ -1610,12 +4671,15 @@
       <c r="C140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>3</v>
+      <c r="T140">
+        <v>1.9806299999999999</v>
+      </c>
+      <c r="U140">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>